--- a/ENTREGA_FINAL/Atlas tracking/2nd_round_lula_vs_flavio_bolsonaro-210720261102.xlsx
+++ b/ENTREGA_FINAL/Atlas tracking/2nd_round_lula_vs_flavio_bolsonaro-210720261102.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AE4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -490,6 +490,9 @@
       <c r="AD1" t="str">
         <v>2026-07-20</v>
       </c>
+      <c r="AE1" t="str">
+        <v>2026-07-27</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -582,6 +585,9 @@
       <c r="AD2">
         <v>48.7</v>
       </c>
+      <c r="AE2">
+        <v>50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -674,6 +680,9 @@
       <c r="AD3">
         <v>43.4</v>
       </c>
+      <c r="AE3">
+        <v>41.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -766,10 +775,13 @@
       <c r="AD4">
         <v>7.9</v>
       </c>
+      <c r="AE4">
+        <v>8.2</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE4"/>
   </ignoredErrors>
 </worksheet>
 </file>